--- a/extenbooks/S1504_extenbook.xlsx
+++ b/extenbooks/S1504_extenbook.xlsx
@@ -13891,7 +13891,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -15380,11 +15380,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15407,64 +15407,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chapter 15 series S1504</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1504_research.json", "adequacy_report": "Technical/docs/chapters/CH15_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1504_DPR.md", "epr": "Technical/docs/series/S1504_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1504_load.py", "processor": "Technical/code/P02_processors/P02_S1504_construct.py", "validator": "Technical/code/V03_validators/V03_S1504_validate.py", "processed": "Technical/data/processed/S1504.parquet", "chopped_csv": "Technical/chopped/S1504.csv", "extenbook_xlsx": "Technical/extenbooks/S1504_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1504_extenbook.xlsx
+++ b/extenbooks/S1504_extenbook.xlsx
@@ -13838,7 +13838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A164"/>
+  <dimension ref="A1:A166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -13877,7 +13877,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Pipeline stage**: Ingestion</t>
         </is>
       </c>
     </row>
@@ -13905,7 +13905,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1. **gGDP** = growth rate of nominal GDP = `ln(GDP_t / GDP_{t-1})` from BEA NIPA T1.1.5 line 1</t>
+          <t>1. **gGDP** = growth rate of nominal GDP = `ln(GDP_t / GDP_{t-1})` from BEA National Income and Product Accounts (NIPA) T1.1.5 line 1</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14001,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shaikh (2016) Figure 15.9 plots gGDP vs pp to illustrate the "new purchasing power" thesis that nominal demand growth equals real growth plus net new credit + net foreign demand.</t>
+          <t>Shaikh (2016) Figures 15.3 and 15.4 plot gGDP vs pp (Figure 15.3 "Growth of Nominal GDP and Relative New Purchasing Power, 1950-2010" as time series; Figure 15.4 the same data as a scatter) to illustrate the "new purchasing power" thesis that nominal demand growth equals real growth plus net new credit + net foreign demand. (Figure 15.9 is the unrelated "Classical and Conventional Phillip-Type Curves" panel — not this series.)</t>
         </is>
       </c>
     </row>
@@ -14041,7 +14041,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>This is a **composite** series — multiple subseries combine into the published variables. The book-period values are taken from `Appendix15_USInflation.xlsx`, which Shaikh compiled by hand from the BEA NIPA + IMF IFS sources below. The replication loads both the chopped values (authoritative for replication) AND attempts a live re-fetch via the modern APIs for cross-validation and extension.</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1504-A, S1504-B); they are listed below.*</t>
         </is>
       </c>
     </row>
@@ -14051,66 +14051,66 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units |</t>
+          <t>This is a **composite** series — multiple subseries combine into the published variables. The book-period values are taken from `Appendix15_USInflation.xlsx`, which Shaikh compiled by hand from the BEA NIPA + IMF IFS sources below. The replication loads both the chopped values (authoritative for replication) AND attempts a live re-fetch via the modern APIs for cross-validation and extension.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>| **S1504-GDP** | 1948-2010 (book), 2011-current (extension) | BEA NIPA T1.1.5 line 1 (Nominal GDP) | USD billions |</t>
+          <t>| Subseries | Coverage | Source | Native units |</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>| **S1504-pGDP** | 1948-2010 | BEA NIPA T1.1.4 (GDP deflator, 2005=100 vintage) | Index |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>| **S1504-CR** | 1948-2010 | Composite: legacy IMF IFS Monetary Survey lines 31 + (78-88) + 79 + 81 = Total Domestic Credit; modern equivalent IMF MFS_DC `DCORP_N_DC` (Depository Corporations Survey: Net Domestic Claims) via `_imf_ifs_resolver.py` | USD millions/billions |</t>
+          <t>| **S1504-GDP** | 1948-2010 (book), 2011-current (extension) | BEA NIPA T1.1.5 line 1 (Nominal GDP) | USD billions |</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>| **S1504-CA** | 1948-2010 | BEA NIPA T4.1 line "Current Account Balance" | USD billions |</t>
+          <t>| **S1504-pGDP** | 1948-2010 | BEA NIPA T1.1.4 (GDP deflator, 2005=100 vintage) | Index |</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>| **S1504-gGDP** | 1949-2010 | derived: `ln(GDP_t / GDP_{t-1})` | Rate (decimal) |</t>
+          <t>| **S1504-CR** | 1948-2010 | Composite: legacy IMF IFS Monetary Survey lines 31 + (78-88) + 79 + 81 = Total Domestic Credit; modern equivalent IMF MFS_DC `DCORP_N_DC` (Depository Corporations Survey: Net Domestic Claims) via `_imf_ifs_resolver.py` | USD millions/billions |</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>| **S1504-pp** | 1949-2010 | derived: `(dCR + CA) / GDP` where `dCR = CR_t - CR_{t-1}` | Rate (decimal) |</t>
+          <t>| **S1504-CA** | 1948-2010 | BEA NIPA T4.1 line "Current Account Balance" | USD billions |</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>| **S1504-gGDP** | 1949-2010 | derived: `ln(GDP_t / GDP_{t-1})` | Rate (decimal) |</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>**Phase 4 typo correction**: dossier originally cited "NIPA Table 1.15"; correct is **NIPA Table 1.1.5**.</t>
+          <t>| **S1504-pp** | 1949-2010 | derived: `(dCR + CA) / GDP` where `dCR = CR_t - CR_{t-1}` | Rate (decimal) |</t>
         </is>
       </c>
     </row>
@@ -14120,7 +14120,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>**Data-adequacy review typo correction**: dossier originally cited "NIPA Table 1.15"; correct is **NIPA Table 1.1.5**.</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>**Composite + formula**. The construction recipe per Appendix 15.1 p.895-896:</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -14140,83 +14140,83 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>**Composite + formula**. The construction recipe per Appendix 15.1 p.895-896:</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>gGDP_t  = ln( GDP_t / GDP_{t-1} )                              (Nominal GDP growth)</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dCR_t   = CR_t - CR_{t-1}                                      (New credit creation)</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PP_t    = dCR_t + CA_t                                         (New purchasing power)</t>
+          <t>gGDP_t  = ln( GDP_t / GDP_{t-1} )                              (Nominal GDP growth)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>pp_t    = PP_t / GDP_t                                          (Relative new purchasing power)</t>
+          <t>dCR_t   = CR_t - CR_{t-1}                                      (New credit creation)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>PP_t    = dCR_t + CA_t                                         (New purchasing power)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>pp_t    = PP_t / GDP_t                                          (Relative new purchasing power)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>The book values are read directly from `Appendix15_USInflation.xlsx` columns `gGDP`, `pp`, `gCR`, etc. for validation. The extension fetches modern equivalents via:</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>- BEA NIPA API (if `BEA_API_KEY` set) for T1.1.5 line 1</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>- IMF MFS_DC `DCORP_N_DC` via `_imf_ifs_resolver.fetch_ifs_series('DCORP_N_DC', 'USA', start, end)` for CR</t>
+          <t>The book values are read directly from `Appendix15_USInflation.xlsx` columns `gGDP`, `pp`, `gCR`, etc. for validation. The extension fetches modern equivalents via:</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>- BEA NIPA API for T4.1 line 29 for CA</t>
+          <t>- BEA NIPA API (if `BEA_API_KEY` set) for T1.1.5 line 1</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>- IMF MFS_DC `DCORP_N_DC` via `_imf_ifs_resolver.fetch_ifs_series('DCORP_N_DC', 'USA', start, end)` for CR</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>- BEA NIPA API for T4.1 line 29 for CA</t>
         </is>
       </c>
     </row>
@@ -14226,24 +14226,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>- **Book period**: 1948-2010 (annual) — 63 obs; growth-rate derivations begin 1949.</t>
         </is>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>- **Extension**: 2011-present. IMF MFS_DC publishes only post-2001 USA data; pre-2001 modern IFS data requires archive bulk download (deferred). Extension status reported per-component.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- **Extension**: 2011-present. IMF MFS_DC publishes only post-2001 USA data; pre-2001 modern IFS data requires archive bulk download (deferred). Extension status reported per-component.</t>
         </is>
       </c>
     </row>
@@ -14253,31 +14253,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>- gGDP: rate (decimal annual log-difference)</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>- pp: rate (decimal, ratio of new purchasing power to GDP)</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>- CR, CA, GDP: nominal USD (millions or billions per source convention; loader normalizes to billions)</t>
+          <t>- gGDP: rate (decimal annual log-difference)</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>- pp: rate (decimal, ratio of new purchasing power to GDP)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>- CR, CA, GDP: nominal USD (millions or billions per source convention; loader normalizes to billions)</t>
         </is>
       </c>
     </row>
@@ -14287,38 +14287,38 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1. **IMF IFS code remap** (NOT a proxy): legacy line numbers 31 + (78-88) + 79 + 81 retired post-2009; modern SDMX 3.0 publishes the same Domestic Claims aggregate under `DCORP_N_DC` in dataflow `MFS_DC`. Recipe in `_imf_ifs_resolver.LINE_TO_MODERN`. Code-remap, not concept substitution; registry records `code_remap: true`.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2. **Pre-2001 IMF IFS coverage gap**: IMF SDMX 3.0 API only publishes USA MFS_DC data from 2001Q1 onwards. The 1948-2000 segment lives only in IMF's archive bulk download or, as here, in Shaikh's hand-compiled values in the chopped table.</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3. **BEA T1.16 line ordering**: not directly used here (used by S1505) but flagged for cross-series consistency.</t>
+          <t>1. **IMF IFS code remap** (NOT a proxy): legacy line numbers 31 + (78-88) + 79 + 81 retired post-2009; modern SDMX (Statistical Data and Metadata eXchange) 3.0 publishes the same Domestic Claims aggregate under `DCORP_N_DC` in dataflow `MFS_DC`. Recipe in `_imf_ifs_resolver.LINE_TO_MODERN`. Code-remap, not concept substitution; registry records `code_remap: true`.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4. **Cross-validation strategy**: if IMF resolver returns data for the 2001-2010 overlap, the validator compares modern `DCORP_N_DC` (USA) against Shaikh's hand-summed CR with +/- 2% tolerance per `_imf_ifs_resolver.validate_against_shaikh`.</t>
+          <t>2. **Pre-2001 IMF IFS coverage gap**: IMF SDMX 3.0 API only publishes USA MFS_DC data from 2001Q1 onwards. The 1948-2000 segment lives only in IMF's archive bulk download or, as here, in Shaikh's hand-compiled values in the chopped table.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3. **BEA T1.16 line ordering**: not directly used here (used by S1505) but flagged for cross-series consistency.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>4. **Cross-validation strategy**: if IMF resolver returns data for the 2001-2010 overlap, the validator compares modern `DCORP_N_DC` (USA) against Shaikh's hand-summed CR with +/- 2% tolerance per `_imf_ifs_resolver.validate_against_shaikh`.</t>
         </is>
       </c>
     </row>
@@ -14328,24 +14328,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>- **CD legacy IDs**: `S083` (gGDP), `S084` (pp)</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figure 15.9; Appendix 15.1 p. 895-896</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>- **Predecessor-build IDs**: `S083` (gGDP), `S084` (pp)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figures 15.3 and 15.4 (p. 704 text); Appendix 15.1 p. 895-896</t>
         </is>
       </c>
     </row>
@@ -14355,89 +14355,89 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>- **Tolerance**: +/- 1.0% per (year, subseries) on the overlap range 1949-2010 against the book's `gGDP` and `pp` columns.</t>
+          <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>- **Expected MAE**: near zero (we read the same precomputed values from the chopped table; recomputation against GDP column is a sanity check).</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>- **Tolerance**: +/- 1.0% per (year, subseries) on the overlap range 1949-2010 against the book's `gGDP` and `pp` columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>- **Expected mean absolute error (MAE)**: near zero (we read the same precomputed values from the chopped table; recomputation against GDP column is a sanity check).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>- **IMF cross-validation (optional)**: +/- 2.0% per year over 2001-2010 if modern API egress is open.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="4">
+    <row r="96">
+      <c r="A96" s="4">
         <f>== EPR: S1504_EPR.md ===</f>
         <v/>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t># S1504 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>**Series**: S1504 — Growth of Nominal GDP and Relative New Purchasing Power</t>
+          <t># S1504 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
+      <c r="A98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>**Construction classification**: `composite` (with derived formulas on top)</t>
+          <t>**Series**: S1504 — Growth of Nominal GDP and Relative New Purchasing Power</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>**Extension method**: re-fetch each component from its modern API (BEA NIPA API for GDP and CA; IMF SDMX 3.0 via `_imf_ifs_resolver.fetch_ifs_series('DCORP_N_DC', 'USA', start, end)` for CR), recompute the formulas</t>
+          <t>**Pipeline stage**: Extension</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Construction classification**: `composite` (with derived formulas on top)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Extension method**: re-fetch each component from its modern API (BEA National Income and Product Accounts (NIPA) API for GDP and CA; IMF SDMX (Statistical Data and Metadata eXchange) 3.0 via `_imf_ifs_resolver.fetch_ifs_series('DCORP_N_DC', 'USA', start, end)` for CR), recompute the formulas</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -14447,7 +14447,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>## 1. Why this series is extendable</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14457,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S1504 is `time_series` + `composite`. All three component sources (BEA NIPA, BEA Current Account, IMF IFS Domestic Claims) are continuously published. The IMF IFS modernization to SDMX 3.0 / `MFS_DC` dataflow is a code remap, not a concept substitution.</t>
+          <t>## 1. Why this series is extendable</t>
         </is>
       </c>
     </row>
@@ -14467,7 +14467,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>S1504 is `time_series` + `composite`. All three component sources (BEA NIPA, BEA Current Account, IMF IFS Domestic Claims) are continuously published. The IMF IFS modernization to SDMX 3.0 / `MFS_DC` dataflow is a code remap, not a concept substitution.</t>
         </is>
       </c>
     </row>
@@ -14477,100 +14477,100 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>INPUTS (book period, authoritative)</t>
-        </is>
-      </c>
+      <c r="A113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1504_book = chopped table Appendix15_USInflation.xlsx columns gGDP, pp, gCR, GDP, CR, CA</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>INPUTS (book period, authoritative)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INPUTS (extension period, re-fetched)</t>
+          <t xml:space="preserve">  S1504_book = chopped table Appendix15_USInflation.xlsx columns gGDP, pp, gCR, GDP, CR, CA</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  BEA_GDP_T115 line 1 (Nominal GDP)</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BEA_CA_T41                 (Current Account Balance)</t>
+          <t>INPUTS (extension period, re-fetched)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IMF MFS_DC DCORP_N_DC USA  (Depository Corporations Survey Net Domestic Claims)</t>
+          <t xml:space="preserve">  BEA_GDP_T115 line 1 (Nominal GDP)</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BEA_CA_T41                 (Current Account Balance)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EXTENSION COMPUTATION (for year t in [2011, current_year])</t>
+          <t xml:space="preserve">  IMF MFS_DC DCORP_N_DC USA  (Depository Corporations Survey Net Domestic Claims)</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  gGDP_t = ln(GDP_t / GDP_{t-1})</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">  dCR_t  = CR_t - CR_{t-1}</t>
+          <t>EXTENSION COMPUTATION (for year t in [2011, current_year])</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">  pp_t   = (dCR_t + CA_t) / GDP_t</t>
+          <t xml:space="preserve">  gGDP_t = ln(GDP_t / GDP_{t-1})</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  dCR_t  = CR_t - CR_{t-1}</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  pp_t   = (dCR_t + CA_t) / GDP_t</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>## 3. IMF IFS resolver integration</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -14580,79 +14580,79 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>## 3. IMF IFS resolver integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>```python</t>
         </is>
       </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>from loaders._imf_ifs_resolver import resolve_ifs_line, fetch_ifs_series</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>from loaders._imf_ifs_resolver import resolve_ifs_line, fetch_ifs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t># Map Shaikh's legacy line 32 (Total Domestic Claims) to modern code</t>
         </is>
       </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>modern_code = resolve_ifs_line(32)   # -&gt; "DCORP_N_DC"</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t># Fetch modern DCS Net Domestic Claims for USA over the overlap+extension window</t>
+          <t>modern_code = resolve_ifs_line(32)   # -&gt; "DCORP_N_DC"</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>fr = fetch_ifs_series("DCORP_N_DC", "USA", 2001, 2025, dataflow="MFS_DC", unit="USD")</t>
-        </is>
-      </c>
+      <c r="A136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>if fr.success:</t>
+          <t># Fetch modern DCS Net Domestic Claims for USA over the overlap+extension window</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">    cr_modern = fr.values   # dict[year, float] in USD</t>
+          <t>fr = fetch_ifs_series("DCORP_N_DC", "USA", 2001, 2025, dataflow="MFS_DC", unit="USD")</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>if fr.success:</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    cr_modern = fr.values   # dict[year, float] in USD</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>## 4. No-proxy disclosure</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14662,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>**Code remap, not proxy.** IMF's own SRF continuity documentation states `DCORP_N_DC` IS the same Depository Corporations Survey Domestic Claims aggregate that Shaikh's 4-line composite (31 + (78-88) + 79 + 81) hand-sums. Registry records `code_remap: true, proxy: false`.</t>
+          <t>## 4. No-proxy disclosure</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>## 5. No-synthetic disclosure</t>
+          <t>**Code remap, not proxy.** IMF's own SRF continuity documentation states `DCORP_N_DC` IS the same Depository Corporations Survey Domestic Claims aggregate that Shaikh's 4-line composite (31 + (78-88) + 79 + 81) hand-sums. Registry records `code_remap: true, proxy: false`.</t>
         </is>
       </c>
     </row>
@@ -14682,7 +14682,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>**None permitted.** If IMF SDMX returns empty for pre-2001 USA, that segment is published as `data_unavailable_pre_2001` — never fabricated.</t>
+          <t>## 5. No-synthetic disclosure</t>
         </is>
       </c>
     </row>
@@ -14692,7 +14692,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>## 6. Failure-mode table</t>
+          <t>**None permitted.** If IMF SDMX returns empty for pre-2001 USA, that segment is published as `data_unavailable_pre_2001` — never fabricated.</t>
         </is>
       </c>
     </row>
@@ -14702,52 +14702,52 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Action |</t>
+          <t>## 6. Failure-mode table</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>| `BEA_API_KEY` missing | `S00_config` | Loader uses chopped values only; extension publishes only the columns recoverable from FRED proxies (GDP available as FRED `GDP`) |</t>
+          <t>| Failure | Detection | Action |</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>| IMF SDMX egress blocked | `fetch_ifs_series.success = False` | CR extension marked `data_unavailable_imf_api_blocked`; book-period CR retained from chopped values |</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>| Pre-2001 IMF data missing | resolver returns no values for years &lt; 2001 | Documented expected; book period uses chopped Shaikh values |</t>
+          <t>| `BEA_API_KEY` missing | `S00_config` | Loader uses chopped values only; extension publishes only the columns recoverable from FRED proxies (GDP available as FRED `GDP`) |</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>| BEA T4.1 line label changed | row-label validation in loader | Warn + skip extension; document in `extension_diagnostics` |</t>
+          <t>| IMF SDMX egress blocked | `fetch_ifs_series.success = False` | CR extension marked `data_unavailable_imf_api_blocked`; book-period CR retained from chopped values |</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>| Pre-2001 IMF data missing | resolver returns no values for years &lt; 2001 | Documented expected; book period uses chopped Shaikh values |</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
+          <t>| BEA T4.1 line label changed | row-label validation in loader | Warn + skip extension; document in `extension_diagnostics` |</t>
         </is>
       </c>
     </row>
@@ -14757,7 +14757,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CD2's S083/S084 used a similar but vintage-different BEA snapshot. gGDP expected to match within ~0.5%; pp may diverge by ~1-2% post-2000 due to BEA Current Account methodology revisions and IMF IFS rebases.</t>
+          <t>## 7. Divergence from the predecessor build</t>
         </is>
       </c>
     </row>
@@ -14767,7 +14767,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>## 8. Validation against Shaikh via resolver</t>
+          <t>The predecessor build's S083/S084 used a similar but vintage-different BEA snapshot. gGDP expected to match within ~0.5%; pp may diverge by ~1-2% post-2000 due to BEA Current Account methodology revisions and IMF IFS rebases.</t>
         </is>
       </c>
     </row>
@@ -14776,6 +14776,16 @@
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
+        <is>
+          <t>## 8. Validation against Shaikh via resolver</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>`_imf_ifs_resolver.validate_against_shaikh(modern_values, shaikh_values, tolerance_pct=2.0)` is called over the 2001-2010 overlap when the API succeeds; the validator's `cd2_comparison` field reports the result for audit.</t>
         </is>
@@ -15365,7 +15375,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T22:14:08.214896+00:00</t>
+          <t>2026-07-02T06:19:40.989371+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1504_extenbook.xlsx
+++ b/extenbooks/S1504_extenbook.xlsx
@@ -13891,7 +13891,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:19:40.989371+00:00</t>
+          <t>2026-07-11T03:44:23.388546+00:00</t>
         </is>
       </c>
     </row>
@@ -15390,11 +15390,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15417,6 +15417,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2016_APPENDIX_15_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>validated_book_and_extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful composite replication of book figure 15.3 (and underlying data for figure 15.4). Operationalizes Shaikh's central inflation variable - relative new purchasing power pp = (domestic credit + current account)/GDP - against nominal GDP growth. Source map (BEA NIPA + IMF IFS) verified against Appendix 15.1. MIXED_UNITS flag is genuine and is resolved here by per-subseries units (levels in USD billions, rates as decimals, deflator as index).", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1504_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1504_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
